--- a/output/pdf_financials_xlsx/MJS.xlsx
+++ b/output/pdf_financials_xlsx/MJS.xlsx
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3.539484</v>
+        <v>-3.43434</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>6.501477</v>
+        <v>-6.465633</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>5.200936</v>
+        <v>-5.362504</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>10.732746</v>
+        <v>-10.304412</v>
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
@@ -1855,16 +1855,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3.486912</v>
+        <v>-3.486912</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>6.483555</v>
+        <v>-6.483555</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.28172</v>
+        <v>-5.28172</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>10.518579</v>
+        <v>-10.518579</v>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3.486912</v>
+        <v>-3.486912</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>6.483555</v>
+        <v>-6.483555</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.28172</v>
+        <v>-5.28172</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>10.518579</v>
+        <v>-10.518579</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -2317,16 +2317,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>58.1152</v>
+        <v>-58.1152</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>162.088875</v>
+        <v>-162.088875</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>264.086</v>
+        <v>-264.086</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>525.92895</v>
+        <v>-525.92895</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -2406,16 +2406,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3.539484</v>
+        <v>-3.43434</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>6.501477</v>
+        <v>-6.465633</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>5.200936</v>
+        <v>-5.362504</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>10.732746</v>
+        <v>-10.304412</v>
       </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3.539484</v>
+        <v>-3.43434</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>6.501477</v>
+        <v>-6.465633</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>5.200936</v>
+        <v>-5.362504</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>10.732746</v>
+        <v>-10.304412</v>
       </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
@@ -2722,16 +2722,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>1.485301247300454</v>
+        <v>-1.530774471950943</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.2756604383896152</v>
+        <v>-0.2771886372146393</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1.553258874940972</v>
+        <v>-1.506460414761462</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1.995453912726529</v>
+        <v>-2.078400980085036</v>
       </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
@@ -6727,52 +6727,52 @@
         <v>1.914373</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>4.256613</v>
+        <v>4.211276</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>9.752613</v>
+        <v>19.857057</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>12.234469</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>13.180353</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>12.488665</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>10.060581</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.934872</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>11.193768</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.178155</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>7.407198</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>12.071824</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>14.094201</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>9.821350000000001</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.183056</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>9.864767000000001</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>17.398713</v>
       </c>
     </row>
     <row r="93">
@@ -12642,7 +12642,11 @@
           <t>Reserves 20</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -15126,7 +15130,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -17230,7 +17238,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -18264,7 +18276,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -19098,7 +19114,11 @@
           <t>Reserves 14</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -20844,7 +20864,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -21898,7 +21922,11 @@
           <t>Reserves 15, 16</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -49092,10 +49120,10 @@
         </is>
       </c>
       <c r="G378" s="5" t="n">
-        <v>5.28172</v>
+        <v>-5.28172</v>
       </c>
       <c r="H378" s="5" t="n">
-        <v>10.518579</v>
+        <v>-10.518579</v>
       </c>
       <c r="I378" t="inlineStr">
         <is>
@@ -51547,10 +51575,10 @@
         </is>
       </c>
       <c r="F401" s="5" t="n">
-        <v>6.483555</v>
+        <v>-6.483555</v>
       </c>
       <c r="G401" s="5" t="n">
-        <v>5.643269</v>
+        <v>-5.643269</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
@@ -53774,10 +53802,10 @@
         </is>
       </c>
       <c r="E422" s="5" t="n">
-        <v>3.486912</v>
+        <v>-3.486912</v>
       </c>
       <c r="F422" s="5" t="n">
-        <v>5.273688</v>
+        <v>-5.273688</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MJS.xlsx
+++ b/output/pdf_financials_xlsx/MJS.xlsx
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003666</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003236</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -2406,10 +2406,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.43434</v>
+        <v>-3.430674</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-6.465633</v>
+        <v>-6.462397</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-5.362504</v>
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.43434</v>
+        <v>-3.430674</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.465633</v>
+        <v>-6.462397</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5.362504</v>
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.679914</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>1.740436</v>
@@ -2920,22 +2920,22 @@
         <v>9.037258</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>10.227054</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>18.842863</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>23.918724</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>33.774231</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>34.867831</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>45.362546</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>97.97146499999999</v>
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.679914</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>1.740436</v>
@@ -3046,22 +3046,22 @@
         <v>9.037258</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>10.227054</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>18.842863</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>23.918724</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>33.774231</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>34.867831</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>7.383</v>
+        <v>52.745546</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>97.97146499999999</v>
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.732106</v>
+        <v>0.052192</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.386449</v>
@@ -3802,22 +3802,22 @@
         <v>5.246314</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>12.716111</v>
+        <v>2.489057</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>23.094723</v>
+        <v>4.25186</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>25.520877</v>
+        <v>1.602153</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>34.238294</v>
+        <v>0.464063</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>35.621208</v>
+        <v>0.753377</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>46.20925</v>
+        <v>0.846704</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0.303801</v>
@@ -10974,7 +10974,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -13860,7 +13864,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -15520,7 +15528,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -17554,7 +17562,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -24376,7 +24384,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -27882,7 +27890,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -53372,7 +53384,7 @@
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E418" s="5" t="n">
